--- a/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/ZW_Requirements_Input.xlsx
+++ b/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/ZW_Requirements_Input.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanmorris/Documents/GitHub/AircraftDesignToolbox/MAIN/Input Excel Sheets/Point Performance Requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01591A84-F50A-5F4F-A971-842A73331CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03F14AF-E9F6-9F4C-B61E-2328853FFD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" activeTab="4" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
+    <workbookView xWindow="-20" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="2" r:id="rId1"/>
-    <sheet name="F16" sheetId="1" r:id="rId2"/>
+    <sheet name="JB.V1" sheetId="10" r:id="rId2"/>
     <sheet name="C172" sheetId="3" r:id="rId3"/>
     <sheet name="B747" sheetId="6" r:id="rId4"/>
     <sheet name="TurboTilt" sheetId="8" r:id="rId5"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="44">
   <si>
     <t>Coef Friction</t>
   </si>
@@ -102,12 +102,6 @@
     <t>Label</t>
   </si>
   <si>
-    <t>TO A</t>
-  </si>
-  <si>
-    <t>TO B</t>
-  </si>
-  <si>
     <t>Stall Velocity</t>
   </si>
   <si>
@@ -144,9 +138,6 @@
     <t>Max Mach</t>
   </si>
   <si>
-    <t>AB</t>
-  </si>
-  <si>
     <t>PROP</t>
   </si>
   <si>
@@ -179,12 +170,15 @@
   <si>
     <t>VTOL Takeoff</t>
   </si>
+  <si>
+    <t>Max Mach (Max Speed)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -206,12 +200,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -226,7 +214,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -239,8 +227,14 @@
         <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -462,11 +456,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -477,8 +508,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -487,7 +518,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -495,9 +526,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2221,7 +2261,7 @@
     <dxf>
       <border outline="0">
         <bottom style="medium">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -2237,7 +2277,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <name val="Arial Unicode MS"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -2275,20 +2315,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}" name="Table3" displayName="Table3" ref="A1:K200" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" tableBorderDxfId="68">
-  <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5EA520BC-547E-FB42-9345-C10BE812E714}" name="Table326" displayName="Table326" ref="A1:K187" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" tableBorderDxfId="26">
+  <autoFilter ref="A1:K187" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F919674C-10DC-DE44-A9F3-90B3D200DA5E}" name="Requirement #" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{CBE9135E-D43C-B64F-82F2-4030E55EBC51}" name="Requirement Type" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{41824150-61A9-7E43-BA0E-0D841F02D9D0}" name="Input 1" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{2CB221DF-97B6-3A4B-AA29-385AAD8EC923}" name="Input 2" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{8A52CDC3-99A4-6F43-8D92-A339D636927D}" name="Input 3" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{14091491-0BCB-3A45-9BC5-4515396CA540}" name="Input 4" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{3E4C5F17-B6DA-944B-9CFE-147012A5B23F}" name="Input 5" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{C85697CD-6A76-EB47-A95B-AE2F7873920E}" name="Input 6" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{818CDA49-0E39-2946-8757-A9D15E8D4A6E}" name="Input 7" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{3F0DAC1D-EB2F-FC4C-AEEC-B9F4795484F8}" name="Input 8" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{34AA4A8F-2A21-874E-9EAF-8ECBDCA330CB}" name="Input 9" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{4E873125-B430-DF47-97E8-8718CA85A22C}" name="Requirement #" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{F52F1F07-B543-0B47-8053-E34E2BA8895A}" name="Requirement Type" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{FE328122-9A74-7A4B-B57D-BF029EDE1844}" name="Input 1" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{418B51CA-8898-B442-BEE4-8304BF1CD6C0}" name="Input 2" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{A456BF20-760C-3A48-A400-7558B03C7A73}" name="Input 3" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{C9B3AF7B-40A5-7A4B-954F-08C72C3E8D95}" name="Input 4" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{A6995574-966C-AA49-8F26-8C85A4851905}" name="Input 5" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{976E4B5C-CC56-E948-9B3D-4F36230C9950}" name="Input 6" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{D10F34FA-7944-934F-B09F-BFE9ED3EFBC2}" name="Input 7" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{C3452EA2-25EF-274F-BAF6-358D378B7C56}" name="Input 8" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{95D5D1CA-CE7A-B245-9964-B82D986B951F}" name="Input 9" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2335,20 +2375,20 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0A78BEFF-89A3-F74D-8EB9-3ED264AED86C}" name="Table325" displayName="Table325" ref="A1:K200" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0A78BEFF-89A3-F74D-8EB9-3ED264AED86C}" name="Table325" displayName="Table325" ref="A1:K200" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" tableBorderDxfId="68">
   <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8E8452FB-D4CF-024D-BED9-0263227800CC}" name="Requirement #" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{09D97C96-66EE-464A-9495-9BC41CC97CDD}" name="Requirement Type" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{C5833324-76B6-ED46-ABE8-8C26CB8A929F}" name="Input 1" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{516580E8-43B2-A94E-BF87-D7CABADDFD20}" name="Input 2" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{D7E38409-68A4-2348-A254-F99A28B3D6AA}" name="Input 3" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{0DA05089-DF15-DA46-B1A0-0DE642F3AB90}" name="Input 4" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{2CCEF327-B870-1046-92B1-14A71A3CA901}" name="Input 5" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{C8111718-8D74-F54C-A527-0FADE5F57B9B}" name="Input 6" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{33F897C6-7671-8849-BBAE-D1E7CF3CB1B0}" name="Input 7" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{91964FF9-90FD-8646-9211-E7DF64E561A3}" name="Input 8" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{C84CDF7D-F0F0-D348-8A57-B96AD3A17DB7}" name="Input 9" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{8E8452FB-D4CF-024D-BED9-0263227800CC}" name="Requirement #" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{09D97C96-66EE-464A-9495-9BC41CC97CDD}" name="Requirement Type" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{C5833324-76B6-ED46-ABE8-8C26CB8A929F}" name="Input 1" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{516580E8-43B2-A94E-BF87-D7CABADDFD20}" name="Input 2" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{D7E38409-68A4-2348-A254-F99A28B3D6AA}" name="Input 3" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{0DA05089-DF15-DA46-B1A0-0DE642F3AB90}" name="Input 4" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{2CCEF327-B870-1046-92B1-14A71A3CA901}" name="Input 5" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{C8111718-8D74-F54C-A527-0FADE5F57B9B}" name="Input 6" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{33F897C6-7671-8849-BBAE-D1E7CF3CB1B0}" name="Input 7" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{91964FF9-90FD-8646-9211-E7DF64E561A3}" name="Input 8" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{C84CDF7D-F0F0-D348-8A57-B96AD3A17DB7}" name="Input 9" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2726,7 +2766,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>13</v>
@@ -2744,7 +2784,7 @@
         <v>16</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H3" s="27" t="s">
         <v>19</v>
@@ -2766,7 +2806,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>1</v>
@@ -2775,7 +2815,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>19</v>
@@ -2800,7 +2840,7 @@
     </row>
     <row r="7" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" s="29" t="s">
         <v>13</v>
@@ -2809,22 +2849,22 @@
         <v>1</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F7" s="29" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="29" t="s">
         <v>27</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>29</v>
       </c>
       <c r="J7" s="29" t="s">
         <v>19</v>
@@ -2844,7 +2884,7 @@
     </row>
     <row r="9" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B9" s="29" t="s">
         <v>13</v>
@@ -2853,22 +2893,22 @@
         <v>1</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F9" s="29" t="s">
         <v>14</v>
       </c>
       <c r="G9" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="29" t="s">
         <v>27</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="29" t="s">
-        <v>29</v>
       </c>
       <c r="J9" s="29" t="s">
         <v>19</v>
@@ -2888,7 +2928,7 @@
     </row>
     <row r="11" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B11" s="29" t="s">
         <v>13</v>
@@ -2897,22 +2937,22 @@
         <v>1</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F11" s="29" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="29" t="s">
         <v>27</v>
-      </c>
-      <c r="H11" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="29" t="s">
-        <v>29</v>
       </c>
       <c r="J11" s="29" t="s">
         <v>19</v>
@@ -2932,7 +2972,7 @@
     </row>
     <row r="13" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B13" s="29" t="s">
         <v>13</v>
@@ -2941,22 +2981,22 @@
         <v>1</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F13" s="29" t="s">
         <v>14</v>
       </c>
       <c r="G13" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="29" t="s">
         <v>27</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13" s="29" t="s">
-        <v>29</v>
       </c>
       <c r="J13" s="29" t="s">
         <v>19</v>
@@ -2976,16 +3016,16 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -3016,8 +3056,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0517A8B8-8768-2C42-BD50-9EE0E108C400}">
-  <dimension ref="A1:K200"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D7EE0F-8787-EE44-845F-537DCD3910B2}">
+  <dimension ref="A1:K187"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="2" customWidth="1"/>
@@ -3025,7 +3065,7 @@
     <col min="3" max="3" width="15.1640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="14" style="2" customWidth="1"/>
     <col min="5" max="5" width="17.83203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="2"/>
+    <col min="6" max="6" width="15" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" style="2" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" style="2" customWidth="1"/>
     <col min="9" max="9" width="19.33203125" style="2" customWidth="1"/>
@@ -3034,7 +3074,7 @@
     <col min="12" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3066,503 +3106,297 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="34">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="B2" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="8" t="s">
+      <c r="D2" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="E2" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="16"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="17"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="H3" s="3">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="I3" s="14">
-        <v>3500</v>
-      </c>
-      <c r="J3" s="3" t="s">
+      <c r="A3" s="34"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37">
+        <v>8000</v>
+      </c>
+      <c r="D3" s="37">
+        <v>1.5</v>
+      </c>
+      <c r="E3" s="37">
+        <v>30.414200000000001</v>
+      </c>
+      <c r="F3" s="37" t="s">
         <v>20</v>
       </c>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
       <c r="K3" s="17"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.20810000000000001</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="34">
+        <v>3</v>
+      </c>
+      <c r="B6" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C6" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D6" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E6" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F6" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G6" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H6" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I6" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J6" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="17"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="H5" s="3">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="I5" s="14">
-        <v>4000</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="17"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="K6" s="17"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="H7" s="3">
-        <v>4500</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="17"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="17"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="3"/>
-      <c r="C9" s="3">
-        <v>5000</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="E9" s="3">
-        <v>160</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="I9" s="14"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="K9" s="17"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
-        <v>5</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="A10" s="4"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="17"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
+      <c r="A11" s="4"/>
       <c r="B11" s="3"/>
-      <c r="C11" s="3">
-        <v>0.85199999999999998</v>
-      </c>
-      <c r="D11" s="3">
-        <v>40000</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="17"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <v>6</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="A12" s="4"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="17"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
+      <c r="A13" s="4"/>
       <c r="B13" s="3"/>
-      <c r="C13" s="3">
-        <v>0.85199999999999998</v>
-      </c>
-      <c r="D13" s="3">
-        <v>35000</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="F13" s="3">
-        <v>1</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="3">
-        <v>1.67</v>
-      </c>
-      <c r="I13" s="3">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="17"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
-        <v>7</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="A14" s="4"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="17"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
+      <c r="A15" s="4"/>
       <c r="B15" s="3"/>
-      <c r="C15" s="3">
-        <v>0.85199999999999998</v>
-      </c>
-      <c r="D15" s="3">
-        <v>20000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="F15" s="3">
-        <v>5</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="17"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
-        <v>8</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>19</v>
-      </c>
+      <c r="A16" s="4"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="17"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
+      <c r="A17" s="4"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="3">
-        <v>0.85199999999999998</v>
-      </c>
-      <c r="D17" s="3">
-        <v>20000</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-      <c r="I17" s="14">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>33</v>
-      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="17"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
+      <c r="A18" s="4"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -3575,7 +3409,7 @@
       <c r="K18" s="17"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
+      <c r="A19" s="4"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -3588,7 +3422,7 @@
       <c r="K19" s="17"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
+      <c r="A20" s="4"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -5758,202 +5592,32 @@
       <c r="J186" s="3"/>
       <c r="K186" s="17"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A187" s="4"/>
-      <c r="B187" s="3"/>
-      <c r="C187" s="3"/>
-      <c r="D187" s="3"/>
-      <c r="E187" s="3"/>
-      <c r="F187" s="3"/>
-      <c r="G187" s="3"/>
-      <c r="H187" s="3"/>
-      <c r="I187" s="14"/>
+    <row r="187" spans="1:11" ht="19" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="12"/>
+      <c r="B187" s="13"/>
+      <c r="C187" s="13"/>
+      <c r="D187" s="13"/>
+      <c r="E187" s="13"/>
+      <c r="F187" s="13"/>
+      <c r="G187" s="13"/>
+      <c r="H187" s="13"/>
+      <c r="I187" s="15"/>
       <c r="J187" s="3"/>
-      <c r="K187" s="17"/>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A188" s="4"/>
-      <c r="B188" s="3"/>
-      <c r="C188" s="3"/>
-      <c r="D188" s="3"/>
-      <c r="E188" s="3"/>
-      <c r="F188" s="3"/>
-      <c r="G188" s="3"/>
-      <c r="H188" s="3"/>
-      <c r="I188" s="14"/>
-      <c r="J188" s="3"/>
-      <c r="K188" s="17"/>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A189" s="4"/>
-      <c r="B189" s="3"/>
-      <c r="C189" s="3"/>
-      <c r="D189" s="3"/>
-      <c r="E189" s="3"/>
-      <c r="F189" s="3"/>
-      <c r="G189" s="3"/>
-      <c r="H189" s="3"/>
-      <c r="I189" s="14"/>
-      <c r="J189" s="3"/>
-      <c r="K189" s="17"/>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A190" s="4"/>
-      <c r="B190" s="3"/>
-      <c r="C190" s="3"/>
-      <c r="D190" s="3"/>
-      <c r="E190" s="3"/>
-      <c r="F190" s="3"/>
-      <c r="G190" s="3"/>
-      <c r="H190" s="3"/>
-      <c r="I190" s="14"/>
-      <c r="J190" s="3"/>
-      <c r="K190" s="17"/>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A191" s="4"/>
-      <c r="B191" s="3"/>
-      <c r="C191" s="3"/>
-      <c r="D191" s="3"/>
-      <c r="E191" s="3"/>
-      <c r="F191" s="3"/>
-      <c r="G191" s="3"/>
-      <c r="H191" s="3"/>
-      <c r="I191" s="14"/>
-      <c r="J191" s="3"/>
-      <c r="K191" s="17"/>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A192" s="4"/>
-      <c r="B192" s="3"/>
-      <c r="C192" s="3"/>
-      <c r="D192" s="3"/>
-      <c r="E192" s="3"/>
-      <c r="F192" s="3"/>
-      <c r="G192" s="3"/>
-      <c r="H192" s="3"/>
-      <c r="I192" s="14"/>
-      <c r="J192" s="3"/>
-      <c r="K192" s="17"/>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A193" s="4"/>
-      <c r="B193" s="3"/>
-      <c r="C193" s="3"/>
-      <c r="D193" s="3"/>
-      <c r="E193" s="3"/>
-      <c r="F193" s="3"/>
-      <c r="G193" s="3"/>
-      <c r="H193" s="3"/>
-      <c r="I193" s="14"/>
-      <c r="J193" s="3"/>
-      <c r="K193" s="17"/>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A194" s="4"/>
-      <c r="B194" s="3"/>
-      <c r="C194" s="3"/>
-      <c r="D194" s="3"/>
-      <c r="E194" s="3"/>
-      <c r="F194" s="3"/>
-      <c r="G194" s="3"/>
-      <c r="H194" s="3"/>
-      <c r="I194" s="14"/>
-      <c r="J194" s="3"/>
-      <c r="K194" s="17"/>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A195" s="4"/>
-      <c r="B195" s="3"/>
-      <c r="C195" s="3"/>
-      <c r="D195" s="3"/>
-      <c r="E195" s="3"/>
-      <c r="F195" s="3"/>
-      <c r="G195" s="3"/>
-      <c r="H195" s="3"/>
-      <c r="I195" s="14"/>
-      <c r="J195" s="3"/>
-      <c r="K195" s="17"/>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A196" s="4"/>
-      <c r="B196" s="3"/>
-      <c r="C196" s="3"/>
-      <c r="D196" s="3"/>
-      <c r="E196" s="3"/>
-      <c r="F196" s="3"/>
-      <c r="G196" s="3"/>
-      <c r="H196" s="3"/>
-      <c r="I196" s="14"/>
-      <c r="J196" s="3"/>
-      <c r="K196" s="17"/>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A197" s="4"/>
-      <c r="B197" s="3"/>
-      <c r="C197" s="3"/>
-      <c r="D197" s="3"/>
-      <c r="E197" s="3"/>
-      <c r="F197" s="3"/>
-      <c r="G197" s="3"/>
-      <c r="H197" s="3"/>
-      <c r="I197" s="14"/>
-      <c r="J197" s="3"/>
-      <c r="K197" s="17"/>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A198" s="4"/>
-      <c r="B198" s="3"/>
-      <c r="C198" s="3"/>
-      <c r="D198" s="3"/>
-      <c r="E198" s="3"/>
-      <c r="F198" s="3"/>
-      <c r="G198" s="3"/>
-      <c r="H198" s="3"/>
-      <c r="I198" s="14"/>
-      <c r="J198" s="3"/>
-      <c r="K198" s="17"/>
-    </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A199" s="4"/>
-      <c r="B199" s="3"/>
-      <c r="C199" s="3"/>
-      <c r="D199" s="3"/>
-      <c r="E199" s="3"/>
-      <c r="F199" s="3"/>
-      <c r="G199" s="3"/>
-      <c r="H199" s="3"/>
-      <c r="I199" s="14"/>
-      <c r="J199" s="3"/>
-      <c r="K199" s="17"/>
-    </row>
-    <row r="200" spans="1:11" ht="19" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="12"/>
-      <c r="B200" s="13"/>
-      <c r="C200" s="13"/>
-      <c r="D200" s="13"/>
-      <c r="E200" s="13"/>
-      <c r="F200" s="13"/>
-      <c r="G200" s="13"/>
-      <c r="H200" s="13"/>
-      <c r="I200" s="15"/>
-      <c r="J200" s="3"/>
-      <c r="K200" s="18"/>
+      <c r="K187" s="18"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A1:B1 D1:XFD1 B2:XFD5 L6:XFD17 B8:K15 F17:K17 B18:XFD21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="12" priority="3">
+  <conditionalFormatting sqref="A1:B1 D1:XFD1 B8:K8 L2:XFD1048576 A9:K1048576 K6:K7 G2:K3">
+    <cfRule type="expression" dxfId="12" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6:I7">
+  <conditionalFormatting sqref="C6:J7">
     <cfRule type="expression" dxfId="11" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D16">
-    <cfRule type="expression" dxfId="10" priority="1">
+  <conditionalFormatting sqref="C4:K5">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6015,7 +5679,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -6061,7 +5725,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F3" s="3">
         <v>2</v>
@@ -6076,7 +5740,7 @@
         <v>2000</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K3" s="17"/>
     </row>
@@ -6085,7 +5749,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>13</v>
@@ -6103,7 +5767,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>19</v>
@@ -6133,7 +5797,7 @@
         <v>1000</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="17"/>
@@ -6143,7 +5807,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
@@ -6152,7 +5816,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>19</v>
@@ -6176,7 +5840,7 @@
         <v>55</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -6189,7 +5853,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>13</v>
@@ -6198,22 +5862,22 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="19" t="s">
         <v>27</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="19" t="s">
-        <v>29</v>
       </c>
       <c r="K8" s="17" t="s">
         <v>19</v>
@@ -6235,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
@@ -6247,7 +5911,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -6255,7 +5919,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>13</v>
@@ -6264,22 +5928,22 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="19" t="s">
         <v>27</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>29</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>19</v>
@@ -6301,7 +5965,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H11" s="3">
         <v>1.67</v>
@@ -6313,7 +5977,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -6321,7 +5985,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>13</v>
@@ -6330,22 +5994,22 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="19" t="s">
         <v>27</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>29</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>19</v>
@@ -6367,7 +6031,7 @@
         <v>1.5</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H13" s="3">
         <v>0</v>
@@ -6379,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -6387,7 +6051,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>13</v>
@@ -6396,22 +6060,22 @@
         <v>1</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="20" t="s">
         <v>27</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="20" t="s">
-        <v>29</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>19</v>
@@ -6433,7 +6097,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -6445,7 +6109,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -8855,17 +8519,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 B2:XFD3 J4:XFD4 K5:XFD5 B6:XFD13 L14:XFD14 F15:XFD21 B16:E21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:I5">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8927,7 +8591,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -8988,7 +8652,7 @@
         <v>10000</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K3" s="17"/>
     </row>
@@ -8997,7 +8661,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>13</v>
@@ -9015,7 +8679,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>19</v>
@@ -9045,7 +8709,7 @@
         <v>3000</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="17"/>
@@ -9055,7 +8719,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
@@ -9064,7 +8728,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>19</v>
@@ -9088,7 +8752,7 @@
         <v>160</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -9101,7 +8765,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>13</v>
@@ -9110,22 +8774,22 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="19" t="s">
         <v>27</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="19" t="s">
-        <v>29</v>
       </c>
       <c r="K8" s="17" t="s">
         <v>19</v>
@@ -9159,7 +8823,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -9167,7 +8831,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>13</v>
@@ -9176,22 +8840,22 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="19" t="s">
         <v>27</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>29</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>19</v>
@@ -9225,7 +8889,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -9233,7 +8897,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>13</v>
@@ -9242,22 +8906,22 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="19" t="s">
         <v>27</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>29</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>19</v>
@@ -9291,7 +8955,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -9299,7 +8963,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>13</v>
@@ -9308,22 +8972,22 @@
         <v>1</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="20" t="s">
         <v>27</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="20" t="s">
-        <v>29</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>19</v>
@@ -9357,7 +9021,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -11767,17 +11431,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 B2:XFD4 C5:XFD5 B6:XFD13 L14:XFD14 F15:XFD21 B16:E21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11839,7 +11503,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -11847,16 +11511,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>19</v>
@@ -11880,7 +11544,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -11893,7 +11557,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
@@ -11902,7 +11566,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>19</v>
@@ -11926,7 +11590,7 @@
         <v>160</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -11939,7 +11603,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>13</v>
@@ -11948,22 +11612,22 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="19" t="s">
         <v>27</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>29</v>
       </c>
       <c r="K6" s="17" t="s">
         <v>19</v>
@@ -11997,7 +11661,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -12005,7 +11669,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>13</v>
@@ -12014,22 +11678,22 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="19" t="s">
         <v>27</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="19" t="s">
-        <v>29</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>19</v>
@@ -12063,7 +11727,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -12071,7 +11735,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>13</v>
@@ -12080,22 +11744,22 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="19" t="s">
         <v>27</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>29</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>19</v>
@@ -12129,7 +11793,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -12137,7 +11801,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>13</v>
@@ -12146,22 +11810,22 @@
         <v>1</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="20" t="s">
         <v>27</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="20" t="s">
-        <v>29</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>19</v>
@@ -12195,7 +11859,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -14631,22 +14295,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 F2:XFD2 B3:XFD3 J4:XFD4 B4:K11 K5:XFD5 B6:XFD13 L14:XFD14 F15:XFD21 B16:E21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:I5">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
